--- a/知识库Excel模板.xlsx
+++ b/知识库Excel模板.xlsx
@@ -7,18 +7,16 @@
     <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整知识库展示模板" sheetId="5" r:id="rId1"/>
-    <sheet name="隐患库模板" sheetId="1" r:id="rId2"/>
-    <sheet name="法律法规库模板" sheetId="2" r:id="rId3"/>
-    <sheet name="隐患法规映射模板" sheetId="3" r:id="rId4"/>
-    <sheet name="隐患案例库模板" sheetId="4" r:id="rId5"/>
+    <sheet name="隐患库模板" sheetId="1" r:id="rId1"/>
+    <sheet name="法律法规库模板" sheetId="2" r:id="rId2"/>
+    <sheet name="隐患案例库模板" sheetId="4" r:id="rId3"/>
+    <sheet name="完整知识库展示模板" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">完整知识库展示模板!$A$1:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">隐患库模板!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">法律法规库模板!$A$1:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">隐患法规映射模板!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">隐患案例库模板!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">隐患库模板!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">法律法规库模板!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">隐患案例库模板!$A$1:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">完整知识库展示模板!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="84">
   <si>
     <t>隐患编码</t>
   </si>
@@ -64,271 +62,232 @@
     <t>整改期限</t>
   </si>
   <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>更新时间</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>更新人</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>FALL-EDGE-001</t>
+  </si>
+  <si>
+    <t>高坠</t>
+  </si>
+  <si>
+    <t>临边洞口</t>
+  </si>
+  <si>
+    <t>临边未设置防护栏杆</t>
+  </si>
+  <si>
+    <t>临边作业区域未设置防护栏杆</t>
+  </si>
+  <si>
+    <t>重大</t>
+  </si>
+  <si>
+    <t>按规范设置双道防护栏杆并设置踢脚板</t>
+  </si>
+  <si>
+    <t>立即整改</t>
+  </si>
+  <si>
+    <t>2026-03-23 10:00:00</t>
+  </si>
+  <si>
+    <t>张三</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>模板示例数据</t>
+  </si>
+  <si>
+    <t>FALL-EDGE-002</t>
+  </si>
+  <si>
+    <t>防护栏杆高度不足</t>
+  </si>
+  <si>
+    <t>防护栏杆高度不足（低于1.2m）</t>
+  </si>
+  <si>
+    <t>加高栏杆至1.2m以上，确保横杆符合要求</t>
+  </si>
+  <si>
+    <t>2026-03-23 10:10:00</t>
+  </si>
+  <si>
+    <t>FALL-EDGE-005</t>
+  </si>
+  <si>
+    <t>洞口未设置防护</t>
+  </si>
+  <si>
+    <t>洞口未设置盖板或防护栏杆</t>
+  </si>
+  <si>
+    <t>根据洞口尺寸设置盖板或防护栏杆，并确保固定牢固</t>
+  </si>
+  <si>
+    <t>2026-03-23 10:20:00</t>
+  </si>
+  <si>
+    <t>条款ID</t>
+  </si>
+  <si>
+    <t>法规名称</t>
+  </si>
+  <si>
+    <t>法规编号</t>
+  </si>
+  <si>
+    <t>条款编号</t>
+  </si>
+  <si>
+    <t>条款内容</t>
+  </si>
+  <si>
+    <t>法规类型</t>
+  </si>
+  <si>
+    <t>STD-001</t>
+  </si>
+  <si>
+    <t>建筑施工高处作业安全技术规范</t>
+  </si>
+  <si>
+    <t>JGJ80-2016</t>
+  </si>
+  <si>
+    <t>第4.1.1条</t>
+  </si>
+  <si>
+    <t>临边作业部位应设置防护栏杆、挡脚板或安全立网等防护设施。</t>
+  </si>
+  <si>
+    <t>行业标准</t>
+  </si>
+  <si>
+    <t>STD-002</t>
+  </si>
+  <si>
+    <t>第4.1.2条</t>
+  </si>
+  <si>
+    <t>防护栏杆高度不得低于1.2m，并应设置水平横杆和踢脚板。</t>
+  </si>
+  <si>
+    <t>STD-003</t>
+  </si>
+  <si>
+    <t>第4.2.1条</t>
+  </si>
+  <si>
+    <t>楼板、屋面和平台等洞口应根据洞口尺寸设置盖板、防护栏杆或安全平网。</t>
+  </si>
+  <si>
+    <t>案例ID</t>
+  </si>
+  <si>
+    <t>事故标题</t>
+  </si>
+  <si>
+    <t>事故摘要</t>
+  </si>
+  <si>
+    <t>事故后果</t>
+  </si>
+  <si>
+    <t>来源链接</t>
+  </si>
+  <si>
+    <t>填充方式</t>
+  </si>
+  <si>
+    <t>CASE-001</t>
+  </si>
+  <si>
+    <t>某工地临边未设防护栏杆致人员坠落事故</t>
+  </si>
+  <si>
+    <t>2024年5月，某工地临边作业区域未设置防护栏杆，作业人员失足坠落。</t>
+  </si>
+  <si>
+    <t>1人死亡</t>
+  </si>
+  <si>
+    <t>https://example.com/case-001</t>
+  </si>
+  <si>
+    <t>人工录入</t>
+  </si>
+  <si>
+    <t>CASE-002</t>
+  </si>
+  <si>
+    <t>某项目防护栏杆高度不足致高处坠落事故</t>
+  </si>
+  <si>
+    <t>2024年6月，某建筑项目临边防护栏杆高度不足，作业人员翻越区域后坠落。</t>
+  </si>
+  <si>
+    <t>https://example.com/case-002</t>
+  </si>
+  <si>
+    <t>AI搜索</t>
+  </si>
+  <si>
+    <t>CASE-003</t>
+  </si>
+  <si>
+    <t>某楼板洞口未防护致人员坠入受伤事故</t>
+  </si>
+  <si>
+    <t>2023年11月，某工地楼板预留洞口未设置防护措施，夜间作业人员坠入洞口受伤。</t>
+  </si>
+  <si>
+    <t>1人重伤</t>
+  </si>
+  <si>
+    <t>https://example.com/case-003</t>
+  </si>
+  <si>
     <t>法规名称/编号/条款</t>
   </si>
   <si>
-    <t>条款内容</t>
-  </si>
-  <si>
-    <t>法规类型</t>
-  </si>
-  <si>
     <t>警示案例</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>FALL-EDGE-001</t>
-  </si>
-  <si>
-    <t>高坠</t>
-  </si>
-  <si>
-    <t>临边洞口</t>
-  </si>
-  <si>
-    <t>临边未设置防护栏杆</t>
-  </si>
-  <si>
-    <t>临边作业区域未设置防护栏杆</t>
-  </si>
-  <si>
-    <t>重大</t>
-  </si>
-  <si>
-    <t>按规范设置双道防护栏杆并设置踢脚板</t>
-  </si>
-  <si>
-    <t>立即整改</t>
-  </si>
-  <si>
     <t>建筑施工高处作业安全技术规范（JGJ80-2016） 第4.1.1条</t>
   </si>
   <si>
-    <t>临边作业部位应设置防护栏杆、挡脚板或安全立网等防护设施。</t>
-  </si>
-  <si>
-    <t>行业标准</t>
-  </si>
-  <si>
     <t>某工地临边未设防护栏杆致人员坠落事故 2024年5月，某工地临边作业区域未设置防护栏杆，作业人员失足坠落。 1人死亡 https://example.com/case-001</t>
   </si>
   <si>
-    <t>模板示例数据</t>
-  </si>
-  <si>
-    <t>FALL-EDGE-002</t>
-  </si>
-  <si>
-    <t>防护栏杆高度不足</t>
-  </si>
-  <si>
-    <t>防护栏杆高度不足（低于1.2m）</t>
-  </si>
-  <si>
-    <t>加高栏杆至1.2m以上，确保横杆符合要求</t>
-  </si>
-  <si>
     <t>建筑施工高处作业安全技术规范（JGJ80-2016） 第4.1.2条</t>
   </si>
   <si>
-    <t>防护栏杆高度不得低于1.2m，并应设置水平横杆和踢脚板。</t>
-  </si>
-  <si>
     <t>某项目防护栏杆高度不足致高处坠落事故 2024年6月，某建筑项目临边防护栏杆高度不足，作业人员翻越区域后坠落。 1人死亡 https://example.com/case-002</t>
   </si>
   <si>
-    <t>FALL-EDGE-005</t>
-  </si>
-  <si>
-    <t>洞口未设置防护</t>
-  </si>
-  <si>
-    <t>洞口未设置盖板或防护栏杆</t>
-  </si>
-  <si>
-    <t>根据洞口尺寸设置盖板或防护栏杆，并确保固定牢固</t>
-  </si>
-  <si>
     <t>建筑施工高处作业安全技术规范（JGJ80-2016） 第4.2.1条</t>
   </si>
   <si>
-    <t>楼板、屋面和平台等洞口应根据洞口尺寸设置盖板、防护栏杆或安全平网。</t>
-  </si>
-  <si>
     <t>某楼板洞口未防护致人员坠入受伤事故 2023年11月，某工地楼板预留洞口未设置防护措施，夜间作业人员坠入洞口受伤。 1人重伤 https://example.com/case-003</t>
-  </si>
-  <si>
-    <t>创建时间</t>
-  </si>
-  <si>
-    <t>更新时间</t>
-  </si>
-  <si>
-    <t>创建人</t>
-  </si>
-  <si>
-    <t>更新人</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>2026-03-23 10:00:00</t>
-  </si>
-  <si>
-    <t>张三</t>
-  </si>
-  <si>
-    <t>启用</t>
-  </si>
-  <si>
-    <t>2026-03-23 10:10:00</t>
-  </si>
-  <si>
-    <t>2026-03-23 10:20:00</t>
-  </si>
-  <si>
-    <t>条款ID</t>
-  </si>
-  <si>
-    <t>法规名称</t>
-  </si>
-  <si>
-    <t>法规编号</t>
-  </si>
-  <si>
-    <t>条款编号</t>
-  </si>
-  <si>
-    <t>生效日期</t>
-  </si>
-  <si>
-    <t>废止日期</t>
-  </si>
-  <si>
-    <t>STD-001</t>
-  </si>
-  <si>
-    <t>建筑施工高处作业安全技术规范</t>
-  </si>
-  <si>
-    <t>JGJ80-2016</t>
-  </si>
-  <si>
-    <t>第4.1.1条</t>
-  </si>
-  <si>
-    <t>2016-12-01</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>STD-002</t>
-  </si>
-  <si>
-    <t>第4.1.2条</t>
-  </si>
-  <si>
-    <t>STD-003</t>
-  </si>
-  <si>
-    <t>第4.2.1条</t>
-  </si>
-  <si>
-    <t>映射ID</t>
-  </si>
-  <si>
-    <t>关联类型</t>
-  </si>
-  <si>
-    <t>MAP-001</t>
-  </si>
-  <si>
-    <t>主要依据</t>
-  </si>
-  <si>
-    <t>对应临边未设置防护栏杆</t>
-  </si>
-  <si>
-    <t>MAP-002</t>
-  </si>
-  <si>
-    <t>对应防护栏杆高度不足</t>
-  </si>
-  <si>
-    <t>MAP-003</t>
-  </si>
-  <si>
-    <t>对应洞口未设置防护</t>
-  </si>
-  <si>
-    <t>案例ID</t>
-  </si>
-  <si>
-    <t>事故标题</t>
-  </si>
-  <si>
-    <t>事故摘要</t>
-  </si>
-  <si>
-    <t>事故后果</t>
-  </si>
-  <si>
-    <t>来源链接</t>
-  </si>
-  <si>
-    <t>填充方式</t>
-  </si>
-  <si>
-    <t>CASE-001</t>
-  </si>
-  <si>
-    <t>某工地临边未设防护栏杆致人员坠落事故</t>
-  </si>
-  <si>
-    <t>2024年5月，某工地临边作业区域未设置防护栏杆，作业人员失足坠落。</t>
-  </si>
-  <si>
-    <t>1人死亡</t>
-  </si>
-  <si>
-    <t>https://example.com/case-001</t>
-  </si>
-  <si>
-    <t>人工录入</t>
-  </si>
-  <si>
-    <t>CASE-002</t>
-  </si>
-  <si>
-    <t>某项目防护栏杆高度不足致高处坠落事故</t>
-  </si>
-  <si>
-    <t>2024年6月，某建筑项目临边防护栏杆高度不足，作业人员翻越区域后坠落。</t>
-  </si>
-  <si>
-    <t>https://example.com/case-002</t>
-  </si>
-  <si>
-    <t>AI搜索</t>
-  </si>
-  <si>
-    <t>CASE-003</t>
-  </si>
-  <si>
-    <t>某楼板洞口未防护致人员坠入受伤事故</t>
-  </si>
-  <si>
-    <t>2023年11月，某工地楼板预留洞口未设置防护措施，夜间作业人员坠入洞口受伤。</t>
-  </si>
-  <si>
-    <t>1人重伤</t>
-  </si>
-  <si>
-    <t>https://example.com/case-003</t>
   </si>
 </sst>
 </file>
@@ -958,10 +917,10 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1527,6 +1486,566 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="23.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="22.6" customWidth="1"/>
+    <col min="5" max="5" width="32.5428571428571" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="53.5714285714286" customWidth="1"/>
+    <col min="8" max="8" width="17.2857142857143" customWidth="1"/>
+    <col min="9" max="10" width="23" customWidth="1"/>
+    <col min="11" max="14" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="1" ht="33" customHeight="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="24" customHeight="1" spans="1:14">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="24" customHeight="1" spans="1:14">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="24" customHeight="1" spans="1:14">
+      <c r="A4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N4" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="34.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="80" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="23" customWidth="1"/>
+    <col min="10" max="11" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="1" ht="32" customHeight="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="32" customHeight="1" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="32" customHeight="1" spans="1:11">
+      <c r="A3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="32" customHeight="1" spans="1:11">
+      <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K4" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="33" customHeight="1" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="12" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17" style="2" customWidth="1"/>
+    <col min="3" max="3" width="41.2857142857143" style="2" customWidth="1"/>
+    <col min="4" max="4" width="81.1428571428571" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12" style="2" customWidth="1"/>
+    <col min="8" max="9" width="23" style="2" customWidth="1"/>
+    <col min="10" max="12" width="12" style="2" customWidth="1"/>
+    <col min="13" max="13" width="15" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:13">
+      <c r="A2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:13">
+      <c r="A3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:13">
+      <c r="A4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M4" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
@@ -1544,890 +2063,166 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
+      <c r="I1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="G2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="I2" s="3" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>23</v>
+        <v>50</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1" spans="1:13">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>20</v>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>23</v>
+        <v>53</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M4" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="53.5714285714286" customWidth="1"/>
-    <col min="8" max="8" width="17.2857142857143" customWidth="1"/>
-    <col min="9" max="10" width="23" customWidth="1"/>
-    <col min="11" max="14" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:14">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="24" customHeight="1" spans="1:14">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="24" customHeight="1" spans="1:14">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="24" customHeight="1" spans="1:14">
-      <c r="A4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N4" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="37" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="11" width="23" customWidth="1"/>
-    <col min="12" max="13" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="32" customHeight="1" spans="1:13">
-      <c r="A1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="32" customHeight="1" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="32" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="32" customHeight="1" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M4" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="27" customHeight="1" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="6" width="23" style="1" customWidth="1"/>
-    <col min="7" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I4" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="33" customHeight="1" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22" style="1" customWidth="1"/>
-    <col min="4" max="4" width="43" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="9" width="23" style="1" customWidth="1"/>
-    <col min="10" max="13" width="12" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" customHeight="1" spans="1:13">
-      <c r="A1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
